--- a/server/src/templates/bills_templates.xlsx
+++ b/server/src/templates/bills_templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\lims-v2\server\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA6892B-23EC-439D-A26F-B866F62379A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B19437-F82B-40DC-9F55-F9FAACB2B1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -231,72 +231,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>在甲乙双方平等自愿、协商一致的原则下，根据甲方要求已完成分析测试服务，截至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>03</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>04</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日，甲方测试清单及收费情况总如下。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b/>
         <sz val="13"/>
         <color theme="1"/>
@@ -541,6 +475,20 @@
   <si>
     <t xml:space="preserve">备注
 </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在甲乙双方平等自愿、协商一致的原则下，根据甲方要求已完成分析测试服务，甲方测试清单及收费情况总如下。</t>
+    </r>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -860,6 +808,78 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -874,78 +894,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1302,120 +1250,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
     </row>
     <row r="2" spans="1:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
     </row>
     <row r="4" spans="1:13" ht="10.7" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+    </row>
+    <row r="6" spans="1:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-    </row>
-    <row r="6" spans="1:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
     </row>
     <row r="7" spans="1:13" s="1" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="E7" s="32"/>
+      <c r="F7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="24"/>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="24"/>
-      <c r="I7" s="40" t="s">
+      <c r="H7" s="32"/>
+      <c r="I7" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="41" t="s">
+      <c r="L7" s="15" t="s">
         <v>27</v>
-      </c>
-      <c r="L7" s="42" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="1" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1423,191 +1371,191 @@
         <v>45490</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="D8" s="9">
         <v>100</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="9">
         <v>1</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="27">
+        <v>15</v>
+      </c>
+      <c r="I8" s="36">
         <v>100</v>
       </c>
-      <c r="J8" s="28"/>
+      <c r="J8" s="37"/>
       <c r="K8" s="12">
         <v>80</v>
       </c>
       <c r="L8" s="10"/>
     </row>
     <row r="9" spans="1:13" s="1" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22">
+      <c r="A9" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="30">
         <v>68240</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
     </row>
     <row r="10" spans="1:13" s="1" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="22">
+        <v>17</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="30">
         <v>4094.4</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
     </row>
     <row r="11" spans="1:13" s="1" customFormat="1" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="30">
+        <v>72334.399999999994</v>
+      </c>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+    </row>
+    <row r="12" spans="1:13" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22">
-        <v>72334.399999999994</v>
-      </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-    </row>
-    <row r="12" spans="1:13" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19" t="s">
+      <c r="B12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="30">
+        <v>68717.679999999993</v>
+      </c>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="13"/>
+    </row>
+    <row r="13" spans="1:13" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22">
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20">
         <v>68717.679999999993</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="13"/>
-    </row>
-    <row r="13" spans="1:13" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" spans="1:13" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="31">
-        <v>68717.679999999993</v>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="13"/>
-    </row>
-    <row r="14" spans="1:13" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="34" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" spans="1:13" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="13"/>
-    </row>
-    <row r="15" spans="1:13" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="37" t="s">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" spans="1:13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="13"/>
-    </row>
-    <row r="16" spans="1:13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="39" t="s">
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" spans="1:13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="13"/>
-    </row>
-    <row r="17" spans="1:13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
       <c r="M17" s="13"/>
     </row>
     <row r="18" spans="1:13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1770,29 +1718,29 @@
     <row r="35" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:L12"/>
     <mergeCell ref="A17:L17"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:L13"/>
     <mergeCell ref="A14:L14"/>
     <mergeCell ref="A15:L15"/>
     <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:L10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:L11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:L12"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:L9"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A6:L6"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <dataValidations count="2">
